--- a/templates/AI実装講座_成果物テンプレート.xlsx
+++ b/templates/AI実装講座_成果物テンプレート.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="261">
   <si>
     <r>
       <rPr>
@@ -3738,7 +3738,110 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">個人名義の契約が残っていないかを必ず洗ってください。社長個人のカードで契約したまま社員が使っている状態は珍しくありません。</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個人名義の契約が残っていないかを必ず洗ってください。社長個人のカードで契約したまま社員が使っている状態は珍しくありません。月額はドル建ての場合があるので、請求書の実額を入れてください（記入例の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ChatGPT Business</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">席あたり月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・年払い</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、最低</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">席から）。</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">サービス名</t>
@@ -4016,6 +4119,36 @@
   </si>
   <si>
     <t xml:space="preserve">月額費用（円）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">⑫権限・費用管理表の合計。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">従量課金がある場合は前月の実績を足す</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">金額効果（月・円）</t>
@@ -4745,7 +4878,7 @@
     <numFmt numFmtId="167" formatCode="General"/>
     <numFmt numFmtId="168" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4946,6 +5079,19 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -5028,7 +5174,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5218,6 +5364,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5849,7 +5999,7 @@
         <v>196</v>
       </c>
       <c r="D5" s="40" t="n">
-        <v>3800</v>
+        <v>11000</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>3</v>
@@ -6168,19 +6318,22 @@
         <f aca="false">⑫権限・費用管理表!D21</f>
         <v>0</v>
       </c>
+      <c r="F12" s="48" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D13" s="48" t="str">
+        <v>222</v>
+      </c>
+      <c r="D13" s="49" t="str">
         <f aca="false">IF(COUNT(D5,F5)=2,(D5-F5)*D11-D12,"")</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="39" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D14" s="47" t="str">
         <f aca="false">IF(D13="","",D13*12)</f>
@@ -6189,7 +6342,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="31" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -6227,7 +6380,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6238,7 +6391,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="21" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
@@ -6248,239 +6401,239 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>174</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="50" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="51"/>
+        <v>235</v>
+      </c>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="52"/>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="49" t="n">
+      <c r="B6" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>237</v>
+      </c>
+      <c r="E6" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="D6" s="44" t="s">
-        <v>236</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="52"/>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D7" s="44" t="s">
-        <v>238</v>
-      </c>
-      <c r="E7" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="51"/>
+      <c r="E7" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="50" t="n">
         <v>4</v>
       </c>
       <c r="C8" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>242</v>
+      </c>
+      <c r="E8" s="53" t="s">
         <v>240</v>
       </c>
-      <c r="D8" s="44" t="s">
-        <v>241</v>
-      </c>
-      <c r="E8" s="52" t="s">
-        <v>239</v>
-      </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="50" t="n">
         <v>5</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>243</v>
-      </c>
-      <c r="E9" s="52" t="s">
-        <v>239</v>
-      </c>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="51"/>
+        <v>244</v>
+      </c>
+      <c r="E9" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="52"/>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="50" t="n">
         <v>6</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="51"/>
+        <v>235</v>
+      </c>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="52"/>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="50" t="n">
         <v>7</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>246</v>
-      </c>
-      <c r="D11" s="53" t="s">
         <v>247</v>
       </c>
-      <c r="E11" s="52" t="s">
-        <v>239</v>
-      </c>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="51"/>
+      <c r="D11" s="54" t="s">
+        <v>248</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="52"/>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="49" t="n">
+      <c r="B12" s="50" t="n">
         <v>8</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>248</v>
-      </c>
-      <c r="D12" s="53" t="s">
         <v>249</v>
       </c>
+      <c r="D12" s="54" t="s">
+        <v>250</v>
+      </c>
       <c r="E12" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="51"/>
+        <v>235</v>
+      </c>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="52"/>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="50" t="n">
         <v>9</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="51"/>
+        <v>235</v>
+      </c>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="52"/>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="49" t="n">
+      <c r="B14" s="50" t="n">
         <v>10</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="51"/>
+        <v>235</v>
+      </c>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="52"/>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="49" t="n">
+      <c r="B15" s="50" t="n">
         <v>11</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="51"/>
+        <v>235</v>
+      </c>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="52"/>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="49" t="n">
+      <c r="B16" s="50" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D16" s="53" t="s">
         <v>257</v>
       </c>
+      <c r="D16" s="54" t="s">
+        <v>258</v>
+      </c>
       <c r="E16" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="51"/>
+        <v>235</v>
+      </c>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="52"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="38" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="39" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/templates/AI実装講座_成果物テンプレート.xlsx
+++ b/templates/AI実装講座_成果物テンプレート.xlsx
@@ -3898,27 +3898,27 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>類似案件を過去実績から3件探す</t>
+          <t>引き合いから品番・数量・納期を確定する</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>案件条件</t>
+          <t>引き合いの原文</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>類似案件3件</t>
+          <t>確定した条件</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>金額の算出</t>
+          <t>金額を出すこと</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>要：社長が案件の妥当性を見る（← 最上流）</t>
+          <t>要：確定した条件が原文と合っているか（← 最上流）</t>
         </is>
       </c>
     </row>

--- a/templates/AI実装講座_成果物テンプレート.xlsx
+++ b/templates/AI実装講座_成果物テンプレート.xlsx
@@ -20,6 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑫効果測定シート" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="習得チェックリスト" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修了時の引き渡しリスト" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初回_観察記録シート" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -239,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -345,6 +346,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -711,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -944,49 +948,61 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>初回_観察記録シート</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>講師用。初回の通話を切ってから5分以内に埋めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>■ 注意</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>掲載している数値は、記入例のための架空のものです。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>①〜⑫はこの2冊の通し番号です。募集資料の「持ち帰るもの①〜⑦」とは別の番号です。</t>
+          <t>掲載している数値は、記入例のための架空のものです。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>文書型の成果物6点（③社内文書テンプレ3種／⑤自社専用AI仕様書／⑥AI利用ルールv1／⑧自動化フロー設計メモ／⑫推進体制図／3年構想）は、</t>
+          <t>①〜⑫はこの2冊の通し番号です。募集資料の「持ち帰るもの①〜⑦」とは別の番号です。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="3" t="inlineStr">
         <is>
+          <t>文書型の成果物6点（③社内文書テンプレ3種／⑤自社専用AI仕様書／⑥AI利用ルールv1／⑧自動化フロー設計メモ／⑫推進体制図／3年構想）は、</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
           <t>別冊「AI実装講座_成果物テンプレート集_文書編.docx」にあります。この2冊で12回分の成果物がすべて揃います。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C8:F8"/>
+    <mergeCell ref="B31:F31"/>
     <mergeCell ref="C19:F19"/>
-    <mergeCell ref="B27:F27"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C15:F15"/>
@@ -996,6 +1012,7 @@
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C25:F25"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="B30:F30"/>
@@ -2382,6 +2399,410 @@
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t>■ 録画の保存期間は修了後6か月です。期間経過後に削除します。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>講師用　初回120分　観察記録シート（通話を切ってから5分以内に埋める）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>翌日には印象が丸まります。記憶が新しいうちに埋めてください。ここで書いたレベルは仮判定です。確定は第3回終了時。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="B4" s="9" t="inlineStr"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>項　目</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>記入欄</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr"/>
+      <c r="F4" s="9" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>■ 基本</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>受講者（会社名・お名前）</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>実施日</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>同席者（いれば実名と役職）</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>■ 実演観察の8項目（○＝できた／△＝迷った／×＝できなかった）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="B11" s="9" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>観察したこと</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>○△×</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>気づいたこと</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="B12" s="36" t="inlineStr">
+        <is>
+          <t>指示に前提・条件を入れているか</t>
+        </is>
+      </c>
+      <c r="C12" s="50" t="n"/>
+      <c r="D12" s="13" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>出力が違ったとき、自分で直せるか</t>
+        </is>
+      </c>
+      <c r="C13" s="50" t="n"/>
+      <c r="D13" s="13" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>ファイルを添付して読ませられるか</t>
+        </is>
+      </c>
+      <c r="C14" s="50" t="n"/>
+      <c r="D14" s="13" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>出た数字を疑うか（検算する素振り）</t>
+        </is>
+      </c>
+      <c r="C15" s="50" t="n"/>
+      <c r="D15" s="13" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="B16" s="36" t="inlineStr">
+        <is>
+          <t>入れてよい情報の線引きができているか</t>
+        </is>
+      </c>
+      <c r="C16" s="50" t="n"/>
+      <c r="D16" s="13" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>過去のやり取りを再利用しているか</t>
+        </is>
+      </c>
+      <c r="C17" s="50" t="n"/>
+      <c r="D17" s="13" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>うまくいかない理由を言語化できるか</t>
+        </is>
+      </c>
+      <c r="C18" s="50" t="n"/>
+      <c r="D18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="B19" s="36" t="inlineStr">
+        <is>
+          <t>社員に説明できる言葉を持っているか</t>
+        </is>
+      </c>
+      <c r="C19" s="50" t="n"/>
+      <c r="D19" s="13" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>■ 判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>仮レベル（Lv.1〜3。Lv.4以上は聞き取りで判定）</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n"/>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>事前診断の自己申告との、ずれ</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>ずれの方向（見栄で高い／謙遜で低い）</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>■ 環境と体制（2-4の聞き取り）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>契約プラン（Free／Go／Plus／Pro／法人）</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>基盤（Google Workspace／Microsoft 365／どちらでもない）※第7回の分岐がここで決まる</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>管理者権限は誰が持っているか</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>情報管理のルールの有無</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>推進候補者（実名）</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>■ 棚卸しの結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>AI化候補 上位1</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="n"/>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>AI化候補 上位2</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n"/>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>AI化候補 上位3</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="n"/>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>その場で渡した「手応え」は何か</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>■ 設計合意（この4つが未確定なら、その週のうちにメールで確定させる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>到達目標（受講者の言葉で）</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="n"/>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>第6回のお披露目 日程と参加社員</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>第12回のお披露目 日程と参加社員</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="n"/>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>全12回の日程（確定／仮）</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>■ 性格メモ（進め方の調整に使う）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>せっかち／じっくり</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="n"/>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>否定されると止まる／議論を好む</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="n"/>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>数字で動く／人で動く</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>■ 次回までに講師がやること</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="B51" s="19" t="inlineStr"/>
+      <c r="C51" s="13" t="n"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="19" t="inlineStr"/>
+      <c r="C52" s="13" t="n"/>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="B53" s="19" t="inlineStr"/>
+      <c r="C53" s="13" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="31" t="inlineStr">
+        <is>
+          <t>■ この表で判定できるのは Lv.1〜3 までです。Lv.4・Lv.5 は操作の習熟ではなく組織への展開の有無で分かれるため、環境と体制の聞き取りで判定します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="31" t="inlineStr">
+        <is>
+          <t>■ 観察中は「Lv.2ですね」と口に出さないこと。判定は講師の道具であって、受講者に渡すラベルではありません。</t>
         </is>
       </c>
     </row>
